--- a/config/notify_message.xlsx
+++ b/config/notify_message.xlsx
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>スタミナを受け取る</t>
+          <t>获得体力</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>11時にスタミナを受け取る</t>
+          <t>11点收到体力</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>スタミナを受け取る</t>
+          <t>获得体力</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>17時にスタミナを受け取る</t>
+          <t>17点接收体力</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>スタミナをMAXまで回復</t>
+          <t>体力恢复到最大</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>スタミナMAX回復</t>
+          <t>体力MAX恢复</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>鉱山洞窟が奪われた！</t>
+          <t>矿山洞穴被抢走了！</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>鉱山洞窟は%sに占拠されました。{0}産出報酬はメールで配布しました。忘れずにお受け取りください。\n引き続きボクの最強彼女をお楽しみください！</t>
+          <t>矿山洞穴%s被占领了。{0}产出奖励是通过电子邮件发送的。请不要忘记收下。\n请继续享受我的最强女友！</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
